--- a/Streamlit/Bus_Plan_Cleaned.xlsx
+++ b/Streamlit/Bus_Plan_Cleaned.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Project/Project_5/Streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_169D6893125BA40E62355476585DCE3A8743DD3C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_169D6893125BA40E62355476585DCE3A8743DD3C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{662C1A0F-4278-4BD0-BEAC-B3D0CCBF0F03}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2006,6 +2006,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2351,9 +2352,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H721"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2379,7 +2383,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2402,7 +2406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2428,7 +2432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -2451,7 +2455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -2477,7 +2481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2500,7 +2504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2526,7 +2530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -2549,7 +2553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -2575,7 +2579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2598,7 +2602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2624,7 +2628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -2647,7 +2651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2673,7 +2677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -2696,7 +2700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -2722,7 +2726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -2745,7 +2749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -2771,7 +2775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -2794,7 +2798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -2820,7 +2824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -2843,7 +2847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -2869,7 +2873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -2892,7 +2896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -2918,7 +2922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -2941,7 +2945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -2967,7 +2971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -2990,7 +2994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -3016,7 +3020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -3039,7 +3043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -3065,7 +3069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -3088,7 +3092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -3111,7 +3115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -3134,7 +3138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -3160,7 +3164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -3183,7 +3187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -3209,7 +3213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -3235,7 +3239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -3258,7 +3262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -3281,7 +3285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -3307,7 +3311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -3330,7 +3334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -3356,7 +3360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -3379,7 +3383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -3405,7 +3409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -3428,7 +3432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -3454,7 +3458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -3477,7 +3481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>9</v>
       </c>
@@ -3503,7 +3507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>13</v>
       </c>
@@ -3526,7 +3530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -3552,7 +3556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -3575,7 +3579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>8</v>
       </c>
@@ -3598,7 +3602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>8</v>
       </c>
@@ -3621,7 +3625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -3647,7 +3651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>13</v>
       </c>
@@ -3670,7 +3674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -3696,7 +3700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -3719,7 +3723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -3745,7 +3749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -3768,7 +3772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>13</v>
       </c>
@@ -3794,7 +3798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>9</v>
       </c>
@@ -3817,7 +3821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -3843,7 +3847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>13</v>
       </c>
@@ -3869,7 +3873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>13</v>
       </c>
@@ -3892,7 +3896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>9</v>
       </c>
@@ -3915,7 +3919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>8</v>
       </c>
@@ -3938,7 +3942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>9</v>
       </c>
@@ -3964,7 +3968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>13</v>
       </c>
@@ -3987,7 +3991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>13</v>
       </c>
@@ -4013,7 +4017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -4039,7 +4043,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>9</v>
       </c>
@@ -4062,7 +4066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>13</v>
       </c>
@@ -4085,7 +4089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>13</v>
       </c>
@@ -4111,7 +4115,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>9</v>
       </c>
@@ -4134,7 +4138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -4160,7 +4164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>13</v>
       </c>
@@ -4183,7 +4187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>13</v>
       </c>
@@ -4209,7 +4213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>9</v>
       </c>
@@ -4232,7 +4236,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>13</v>
       </c>
@@ -4258,7 +4262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>9</v>
       </c>
@@ -4281,7 +4285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>13</v>
       </c>
@@ -4307,7 +4311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -4330,7 +4334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>13</v>
       </c>
@@ -4356,7 +4360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>9</v>
       </c>
@@ -4379,7 +4383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>13</v>
       </c>
@@ -4405,7 +4409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>9</v>
       </c>
@@ -4428,7 +4432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>13</v>
       </c>
@@ -4454,7 +4458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>9</v>
       </c>
@@ -4477,7 +4481,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>13</v>
       </c>
@@ -4503,7 +4507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>9</v>
       </c>
@@ -4526,7 +4530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>13</v>
       </c>
@@ -4552,7 +4556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>9</v>
       </c>
@@ -4575,7 +4579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>13</v>
       </c>
@@ -4601,7 +4605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>9</v>
       </c>
@@ -4624,7 +4628,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>8</v>
       </c>
@@ -4647,7 +4651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>8</v>
       </c>
@@ -4670,7 +4674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>13</v>
       </c>
@@ -4696,7 +4700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>9</v>
       </c>
@@ -4719,7 +4723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>13</v>
       </c>
@@ -4745,7 +4749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>9</v>
       </c>
@@ -4771,7 +4775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>9</v>
       </c>
@@ -4794,7 +4798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>13</v>
       </c>
@@ -4817,7 +4821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>13</v>
       </c>
@@ -4843,7 +4847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>9</v>
       </c>
@@ -4866,7 +4870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>9</v>
       </c>
@@ -4892,7 +4896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>13</v>
       </c>
@@ -4915,7 +4919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>13</v>
       </c>
@@ -4941,7 +4945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>9</v>
       </c>
@@ -4964,7 +4968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>13</v>
       </c>
@@ -4990,7 +4994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>9</v>
       </c>
@@ -5013,7 +5017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>13</v>
       </c>
@@ -5039,7 +5043,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>9</v>
       </c>
@@ -5062,7 +5066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>9</v>
       </c>
@@ -5088,7 +5092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>13</v>
       </c>
@@ -5111,7 +5115,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>13</v>
       </c>
@@ -5137,7 +5141,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>9</v>
       </c>
@@ -5160,7 +5164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -5183,7 +5187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>8</v>
       </c>
@@ -5206,7 +5210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>9</v>
       </c>
@@ -5232,7 +5236,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>13</v>
       </c>
@@ -5255,7 +5259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>13</v>
       </c>
@@ -5281,7 +5285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>9</v>
       </c>
@@ -5304,7 +5308,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>9</v>
       </c>
@@ -5330,7 +5334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>13</v>
       </c>
@@ -5353,7 +5357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>13</v>
       </c>
@@ -5379,7 +5383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>9</v>
       </c>
@@ -5402,7 +5406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>13</v>
       </c>
@@ -5428,7 +5432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>9</v>
       </c>
@@ -5451,7 +5455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>8</v>
       </c>
@@ -5474,7 +5478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>9</v>
       </c>
@@ -5500,7 +5504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>13</v>
       </c>
@@ -5523,7 +5527,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>13</v>
       </c>
@@ -5549,7 +5553,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>9</v>
       </c>
@@ -5572,7 +5576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>13</v>
       </c>
@@ -5598,7 +5602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>9</v>
       </c>
@@ -5621,7 +5625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -5647,7 +5651,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>13</v>
       </c>
@@ -5670,7 +5674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>13</v>
       </c>
@@ -5696,7 +5700,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>9</v>
       </c>
@@ -5719,7 +5723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>13</v>
       </c>
@@ -5745,7 +5749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>9</v>
       </c>
@@ -5768,7 +5772,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>13</v>
       </c>
@@ -5794,7 +5798,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>9</v>
       </c>
@@ -5817,7 +5821,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>9</v>
       </c>
@@ -5843,7 +5847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>13</v>
       </c>
@@ -5866,7 +5870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>13</v>
       </c>
@@ -5892,7 +5896,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>9</v>
       </c>
@@ -5915,7 +5919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>13</v>
       </c>
@@ -5941,7 +5945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>9</v>
       </c>
@@ -5964,7 +5968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>13</v>
       </c>
@@ -5990,7 +5994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>9</v>
       </c>
@@ -6013,7 +6017,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>13</v>
       </c>
@@ -6039,7 +6043,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>9</v>
       </c>
@@ -6062,7 +6066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>13</v>
       </c>
@@ -6088,7 +6092,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>9</v>
       </c>
@@ -6111,7 +6115,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>13</v>
       </c>
@@ -6137,7 +6141,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>9</v>
       </c>
@@ -6160,7 +6164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>8</v>
       </c>
@@ -6183,7 +6187,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>8</v>
       </c>
@@ -6206,7 +6210,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>13</v>
       </c>
@@ -6232,7 +6236,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>9</v>
       </c>
@@ -6255,7 +6259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>13</v>
       </c>
@@ -6281,7 +6285,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>9</v>
       </c>
@@ -6307,7 +6311,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>9</v>
       </c>
@@ -6330,7 +6334,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>13</v>
       </c>
@@ -6353,7 +6357,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>13</v>
       </c>
@@ -6379,7 +6383,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>9</v>
       </c>
@@ -6402,7 +6406,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>9</v>
       </c>
@@ -6428,7 +6432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>13</v>
       </c>
@@ -6451,7 +6455,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>13</v>
       </c>
@@ -6477,7 +6481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>9</v>
       </c>
@@ -6500,7 +6504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>13</v>
       </c>
@@ -6526,7 +6530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>9</v>
       </c>
@@ -6549,7 +6553,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>9</v>
       </c>
@@ -6575,7 +6579,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>13</v>
       </c>
@@ -6601,7 +6605,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>13</v>
       </c>
@@ -6624,7 +6628,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>9</v>
       </c>
@@ -6647,7 +6651,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>13</v>
       </c>
@@ -6673,7 +6677,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>9</v>
       </c>
@@ -6696,7 +6700,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>8</v>
       </c>
@@ -6719,7 +6723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>8</v>
       </c>
@@ -6742,7 +6746,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>9</v>
       </c>
@@ -6768,7 +6772,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>13</v>
       </c>
@@ -6791,7 +6795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>8</v>
       </c>
@@ -6814,7 +6818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>9</v>
       </c>
@@ -6840,7 +6844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>13</v>
       </c>
@@ -6863,7 +6867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>13</v>
       </c>
@@ -6889,7 +6893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>9</v>
       </c>
@@ -6912,7 +6916,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>13</v>
       </c>
@@ -6938,7 +6942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>9</v>
       </c>
@@ -6961,7 +6965,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>9</v>
       </c>
@@ -6987,7 +6991,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>13</v>
       </c>
@@ -7010,7 +7014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>13</v>
       </c>
@@ -7036,7 +7040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>9</v>
       </c>
@@ -7059,7 +7063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>13</v>
       </c>
@@ -7085,7 +7089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>9</v>
       </c>
@@ -7108,7 +7112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>13</v>
       </c>
@@ -7134,7 +7138,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>9</v>
       </c>
@@ -7157,7 +7161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>9</v>
       </c>
@@ -7183,7 +7187,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>13</v>
       </c>
@@ -7206,7 +7210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>13</v>
       </c>
@@ -7232,7 +7236,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>9</v>
       </c>
@@ -7255,7 +7259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>13</v>
       </c>
@@ -7281,7 +7285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>9</v>
       </c>
@@ -7304,7 +7308,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>13</v>
       </c>
@@ -7330,7 +7334,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>9</v>
       </c>
@@ -7353,7 +7357,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>13</v>
       </c>
@@ -7379,7 +7383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>9</v>
       </c>
@@ -7402,7 +7406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>13</v>
       </c>
@@ -7428,7 +7432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>9</v>
       </c>
@@ -7451,7 +7455,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>13</v>
       </c>
@@ -7477,7 +7481,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>9</v>
       </c>
@@ -7500,7 +7504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>8</v>
       </c>
@@ -7523,7 +7527,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>8</v>
       </c>
@@ -7546,7 +7550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>13</v>
       </c>
@@ -7572,7 +7576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>9</v>
       </c>
@@ -7595,7 +7599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>13</v>
       </c>
@@ -7621,7 +7625,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>9</v>
       </c>
@@ -7644,7 +7648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>9</v>
       </c>
@@ -7670,7 +7674,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>13</v>
       </c>
@@ -7693,7 +7697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>13</v>
       </c>
@@ -7719,7 +7723,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>9</v>
       </c>
@@ -7742,7 +7746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>13</v>
       </c>
@@ -7768,7 +7772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>9</v>
       </c>
@@ -7791,7 +7795,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>8</v>
       </c>
@@ -7814,7 +7818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>8</v>
       </c>
@@ -7837,7 +7841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>9</v>
       </c>
@@ -7863,7 +7867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>13</v>
       </c>
@@ -7886,7 +7890,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>8</v>
       </c>
@@ -7909,7 +7913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>9</v>
       </c>
@@ -7935,7 +7939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>13</v>
       </c>
@@ -7958,7 +7962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>13</v>
       </c>
@@ -7984,7 +7988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>9</v>
       </c>
@@ -8007,7 +8011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>13</v>
       </c>
@@ -8033,7 +8037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>9</v>
       </c>
@@ -8056,7 +8060,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>9</v>
       </c>
@@ -8082,7 +8086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>13</v>
       </c>
@@ -8105,7 +8109,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>13</v>
       </c>
@@ -8131,7 +8135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>9</v>
       </c>
@@ -8154,7 +8158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>13</v>
       </c>
@@ -8180,7 +8184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>9</v>
       </c>
@@ -8203,7 +8207,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>13</v>
       </c>
@@ -8229,7 +8233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>9</v>
       </c>
@@ -8252,7 +8256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>13</v>
       </c>
@@ -8278,7 +8282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>9</v>
       </c>
@@ -8301,7 +8305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>13</v>
       </c>
@@ -8327,7 +8331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>9</v>
       </c>
@@ -8350,7 +8354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>13</v>
       </c>
@@ -8376,7 +8380,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>9</v>
       </c>
@@ -8399,7 +8403,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>13</v>
       </c>
@@ -8425,7 +8429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>9</v>
       </c>
@@ -8448,7 +8452,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>9</v>
       </c>
@@ -8474,7 +8478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>13</v>
       </c>
@@ -8497,7 +8501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>13</v>
       </c>
@@ -8523,7 +8527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>9</v>
       </c>
@@ -8546,7 +8550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>9</v>
       </c>
@@ -8572,7 +8576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>13</v>
       </c>
@@ -8595,7 +8599,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>13</v>
       </c>
@@ -8621,7 +8625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>9</v>
       </c>
@@ -8644,7 +8648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>8</v>
       </c>
@@ -8667,7 +8671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>8</v>
       </c>
@@ -8690,7 +8694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>9</v>
       </c>
@@ -8716,7 +8720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>13</v>
       </c>
@@ -8739,7 +8743,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>13</v>
       </c>
@@ -8765,7 +8769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>9</v>
       </c>
@@ -8788,7 +8792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>9</v>
       </c>
@@ -8814,7 +8818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>13</v>
       </c>
@@ -8837,7 +8841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>13</v>
       </c>
@@ -8863,7 +8867,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>9</v>
       </c>
@@ -8886,7 +8890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>13</v>
       </c>
@@ -8912,7 +8916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>9</v>
       </c>
@@ -8935,7 +8939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>8</v>
       </c>
@@ -8958,7 +8962,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>9</v>
       </c>
@@ -8984,7 +8988,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>13</v>
       </c>
@@ -9007,7 +9011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>13</v>
       </c>
@@ -9033,7 +9037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>9</v>
       </c>
@@ -9056,7 +9060,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>13</v>
       </c>
@@ -9082,7 +9086,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>9</v>
       </c>
@@ -9105,7 +9109,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>13</v>
       </c>
@@ -9131,7 +9135,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>9</v>
       </c>
@@ -9154,7 +9158,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>13</v>
       </c>
@@ -9180,7 +9184,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>9</v>
       </c>
@@ -9203,7 +9207,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>13</v>
       </c>
@@ -9229,7 +9233,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>9</v>
       </c>
@@ -9252,7 +9256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>13</v>
       </c>
@@ -9278,7 +9282,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>9</v>
       </c>
@@ -9301,7 +9305,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>13</v>
       </c>
@@ -9327,7 +9331,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>9</v>
       </c>
@@ -9350,7 +9354,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>13</v>
       </c>
@@ -9376,7 +9380,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>9</v>
       </c>
@@ -9399,7 +9403,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>13</v>
       </c>
@@ -9425,7 +9429,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>9</v>
       </c>
@@ -9448,7 +9452,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>13</v>
       </c>
@@ -9474,7 +9478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>9</v>
       </c>
@@ -9497,7 +9501,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>8</v>
       </c>
@@ -9520,7 +9524,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>8</v>
       </c>
@@ -9543,7 +9547,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>13</v>
       </c>
@@ -9569,7 +9573,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>9</v>
       </c>
@@ -9592,7 +9596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>9</v>
       </c>
@@ -9618,7 +9622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>13</v>
       </c>
@@ -9641,7 +9645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>13</v>
       </c>
@@ -9667,7 +9671,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>9</v>
       </c>
@@ -9690,7 +9694,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>9</v>
       </c>
@@ -9716,7 +9720,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>13</v>
       </c>
@@ -9739,7 +9743,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>13</v>
       </c>
@@ -9765,7 +9769,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>9</v>
       </c>
@@ -9788,7 +9792,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>13</v>
       </c>
@@ -9814,7 +9818,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>9</v>
       </c>
@@ -9837,7 +9841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>9</v>
       </c>
@@ -9863,7 +9867,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>13</v>
       </c>
@@ -9886,7 +9890,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>13</v>
       </c>
@@ -9912,7 +9916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>9</v>
       </c>
@@ -9935,7 +9939,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>8</v>
       </c>
@@ -9958,7 +9962,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>9</v>
       </c>
@@ -9984,7 +9988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>13</v>
       </c>
@@ -10007,7 +10011,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>13</v>
       </c>
@@ -10033,7 +10037,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>9</v>
       </c>
@@ -10056,7 +10060,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>13</v>
       </c>
@@ -10082,7 +10086,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>9</v>
       </c>
@@ -10105,7 +10109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>13</v>
       </c>
@@ -10131,7 +10135,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>9</v>
       </c>
@@ -10154,7 +10158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>13</v>
       </c>
@@ -10180,7 +10184,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>9</v>
       </c>
@@ -10203,7 +10207,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>13</v>
       </c>
@@ -10229,7 +10233,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>9</v>
       </c>
@@ -10252,7 +10256,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>13</v>
       </c>
@@ -10278,7 +10282,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>9</v>
       </c>
@@ -10301,7 +10305,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>13</v>
       </c>
@@ -10327,7 +10331,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>9</v>
       </c>
@@ -10350,7 +10354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>13</v>
       </c>
@@ -10376,7 +10380,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>9</v>
       </c>
@@ -10399,7 +10403,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>13</v>
       </c>
@@ -10425,7 +10429,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>9</v>
       </c>
@@ -10448,7 +10452,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>13</v>
       </c>
@@ -10474,7 +10478,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>9</v>
       </c>
@@ -10497,7 +10501,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>8</v>
       </c>
@@ -10520,7 +10524,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>8</v>
       </c>
@@ -10543,7 +10547,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>13</v>
       </c>
@@ -10569,7 +10573,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>9</v>
       </c>
@@ -10595,7 +10599,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>9</v>
       </c>
@@ -10618,7 +10622,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>13</v>
       </c>
@@ -10641,7 +10645,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>13</v>
       </c>
@@ -10667,7 +10671,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>9</v>
       </c>
@@ -10690,7 +10694,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>13</v>
       </c>
@@ -10716,7 +10720,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>9</v>
       </c>
@@ -10739,7 +10743,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>13</v>
       </c>
@@ -10765,7 +10769,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>9</v>
       </c>
@@ -10788,7 +10792,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>13</v>
       </c>
@@ -10814,7 +10818,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>9</v>
       </c>
@@ -10837,7 +10841,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>9</v>
       </c>
@@ -10863,7 +10867,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>13</v>
       </c>
@@ -10886,7 +10890,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>13</v>
       </c>
@@ -10912,7 +10916,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>9</v>
       </c>
@@ -10935,7 +10939,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>8</v>
       </c>
@@ -10958,7 +10962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>9</v>
       </c>
@@ -10984,7 +10988,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>13</v>
       </c>
@@ -11007,7 +11011,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>13</v>
       </c>
@@ -11033,7 +11037,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>9</v>
       </c>
@@ -11056,7 +11060,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>13</v>
       </c>
@@ -11082,7 +11086,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>9</v>
       </c>
@@ -11105,7 +11109,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>13</v>
       </c>
@@ -11131,7 +11135,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>9</v>
       </c>
@@ -11154,7 +11158,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>13</v>
       </c>
@@ -11180,7 +11184,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>9</v>
       </c>
@@ -11203,7 +11207,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>13</v>
       </c>
@@ -11229,7 +11233,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>9</v>
       </c>
@@ -11252,7 +11256,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>13</v>
       </c>
@@ -11278,7 +11282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>9</v>
       </c>
@@ -11301,7 +11305,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>13</v>
       </c>
@@ -11327,7 +11331,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>9</v>
       </c>
@@ -11350,7 +11354,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>13</v>
       </c>
@@ -11376,7 +11380,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>9</v>
       </c>
@@ -11399,7 +11403,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>13</v>
       </c>
@@ -11425,7 +11429,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>9</v>
       </c>
@@ -11448,7 +11452,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>13</v>
       </c>
@@ -11474,7 +11478,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>9</v>
       </c>
@@ -11497,7 +11501,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>8</v>
       </c>
@@ -11520,7 +11524,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>8</v>
       </c>
@@ -11543,7 +11547,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>9</v>
       </c>
@@ -11569,7 +11573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>13</v>
       </c>
@@ -11592,7 +11596,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>13</v>
       </c>
@@ -11618,7 +11622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>9</v>
       </c>
@@ -11641,7 +11645,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>13</v>
       </c>
@@ -11667,7 +11671,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>9</v>
       </c>
@@ -11690,7 +11694,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>13</v>
       </c>
@@ -11716,7 +11720,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>9</v>
       </c>
@@ -11739,7 +11743,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>13</v>
       </c>
@@ -11765,7 +11769,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>9</v>
       </c>
@@ -11788,7 +11792,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>9</v>
       </c>
@@ -11814,7 +11818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>13</v>
       </c>
@@ -11837,7 +11841,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>13</v>
       </c>
@@ -11863,7 +11867,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>9</v>
       </c>
@@ -11886,7 +11890,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>9</v>
       </c>
@@ -11912,7 +11916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>13</v>
       </c>
@@ -11935,7 +11939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>8</v>
       </c>
@@ -11958,7 +11962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>9</v>
       </c>
@@ -11984,7 +11988,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>13</v>
       </c>
@@ -12007,7 +12011,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>13</v>
       </c>
@@ -12033,7 +12037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>9</v>
       </c>
@@ -12056,7 +12060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>9</v>
       </c>
@@ -12082,7 +12086,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>13</v>
       </c>
@@ -12105,7 +12109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>13</v>
       </c>
@@ -12131,7 +12135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>9</v>
       </c>
@@ -12154,7 +12158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>9</v>
       </c>
@@ -12180,7 +12184,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>13</v>
       </c>
@@ -12203,7 +12207,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>13</v>
       </c>
@@ -12229,7 +12233,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>9</v>
       </c>
@@ -12252,7 +12256,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>9</v>
       </c>
@@ -12278,7 +12282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>13</v>
       </c>
@@ -12301,7 +12305,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>13</v>
       </c>
@@ -12327,7 +12331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>9</v>
       </c>
@@ -12350,7 +12354,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>9</v>
       </c>
@@ -12376,7 +12380,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>13</v>
       </c>
@@ -12399,7 +12403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>13</v>
       </c>
@@ -12425,7 +12429,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>9</v>
       </c>
@@ -12448,7 +12452,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>9</v>
       </c>
@@ -12474,7 +12478,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>13</v>
       </c>
@@ -12497,7 +12501,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>13</v>
       </c>
@@ -12523,7 +12527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>9</v>
       </c>
@@ -12546,7 +12550,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>9</v>
       </c>
@@ -12572,7 +12576,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>13</v>
       </c>
@@ -12595,7 +12599,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>13</v>
       </c>
@@ -12621,7 +12625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>9</v>
       </c>
@@ -12647,7 +12651,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>9</v>
       </c>
@@ -12670,7 +12674,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>13</v>
       </c>
@@ -12693,7 +12697,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>13</v>
       </c>
@@ -12719,7 +12723,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>9</v>
       </c>
@@ -12742,7 +12746,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>13</v>
       </c>
@@ -12768,7 +12772,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>9</v>
       </c>
@@ -12791,7 +12795,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>13</v>
       </c>
@@ -12817,7 +12821,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>9</v>
       </c>
@@ -12840,7 +12844,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>8</v>
       </c>
@@ -12863,7 +12867,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>8</v>
       </c>
@@ -12886,7 +12890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>13</v>
       </c>
@@ -12912,7 +12916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>9</v>
       </c>
@@ -12935,7 +12939,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>9</v>
       </c>
@@ -12961,7 +12965,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>13</v>
       </c>
@@ -12984,7 +12988,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>13</v>
       </c>
@@ -13010,7 +13014,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>9</v>
       </c>
@@ -13033,7 +13037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>9</v>
       </c>
@@ -13059,7 +13063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>13</v>
       </c>
@@ -13082,7 +13086,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>8</v>
       </c>
@@ -13105,7 +13109,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>9</v>
       </c>
@@ -13131,7 +13135,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>13</v>
       </c>
@@ -13154,7 +13158,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>13</v>
       </c>
@@ -13180,7 +13184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>9</v>
       </c>
@@ -13203,7 +13207,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>9</v>
       </c>
@@ -13229,7 +13233,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>13</v>
       </c>
@@ -13252,7 +13256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>13</v>
       </c>
@@ -13278,7 +13282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>9</v>
       </c>
@@ -13301,7 +13305,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>9</v>
       </c>
@@ -13327,7 +13331,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>13</v>
       </c>
@@ -13350,7 +13354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>13</v>
       </c>
@@ -13376,7 +13380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>9</v>
       </c>
@@ -13399,7 +13403,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>9</v>
       </c>
@@ -13425,7 +13429,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>13</v>
       </c>
@@ -13448,7 +13452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>13</v>
       </c>
@@ -13474,7 +13478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>9</v>
       </c>
@@ -13497,7 +13501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>9</v>
       </c>
@@ -13523,7 +13527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>13</v>
       </c>
@@ -13546,7 +13550,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>13</v>
       </c>
@@ -13572,7 +13576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>9</v>
       </c>
@@ -13595,7 +13599,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>9</v>
       </c>
@@ -13621,7 +13625,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>13</v>
       </c>
@@ -13644,7 +13648,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>13</v>
       </c>
@@ -13670,7 +13674,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>9</v>
       </c>
@@ -13696,7 +13700,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>9</v>
       </c>
@@ -13719,7 +13723,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>13</v>
       </c>
@@ -13742,7 +13746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>13</v>
       </c>
@@ -13768,7 +13772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>9</v>
       </c>
@@ -13791,7 +13795,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>13</v>
       </c>
@@ -13817,7 +13821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>9</v>
       </c>
@@ -13840,7 +13844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>9</v>
       </c>
@@ -13866,7 +13870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>13</v>
       </c>
@@ -13889,7 +13893,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>13</v>
       </c>
@@ -13915,7 +13919,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>9</v>
       </c>
@@ -13938,7 +13942,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>9</v>
       </c>
@@ -13964,7 +13968,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>13</v>
       </c>
@@ -13987,7 +13991,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>13</v>
       </c>
@@ -14013,7 +14017,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>9</v>
       </c>
@@ -14036,7 +14040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>8</v>
       </c>
@@ -14059,7 +14063,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>8</v>
       </c>
@@ -14082,7 +14086,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>9</v>
       </c>
@@ -14108,7 +14112,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>13</v>
       </c>
@@ -14131,7 +14135,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>9</v>
       </c>
@@ -14157,7 +14161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>13</v>
       </c>
@@ -14180,7 +14184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>8</v>
       </c>
@@ -14203,7 +14207,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>9</v>
       </c>
@@ -14229,7 +14233,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>13</v>
       </c>
@@ -14252,7 +14256,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>9</v>
       </c>
@@ -14278,7 +14282,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>13</v>
       </c>
@@ -14301,7 +14305,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>9</v>
       </c>
@@ -14327,7 +14331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>13</v>
       </c>
@@ -14350,7 +14354,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>9</v>
       </c>
@@ -14376,7 +14380,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>13</v>
       </c>
@@ -14399,7 +14403,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>9</v>
       </c>
@@ -14425,7 +14429,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>13</v>
       </c>
@@ -14448,7 +14452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>9</v>
       </c>
@@ -14474,7 +14478,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>13</v>
       </c>
@@ -14497,7 +14501,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>9</v>
       </c>
@@ -14523,7 +14527,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>13</v>
       </c>
@@ -14546,7 +14550,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>9</v>
       </c>
@@ -14572,7 +14576,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>13</v>
       </c>
@@ -14595,7 +14599,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>13</v>
       </c>
@@ -14621,7 +14625,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>9</v>
       </c>
@@ -14644,7 +14648,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>9</v>
       </c>
@@ -14670,7 +14674,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>13</v>
       </c>
@@ -14693,7 +14697,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>13</v>
       </c>
@@ -14719,7 +14723,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>9</v>
       </c>
@@ -14742,7 +14746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>9</v>
       </c>
@@ -14768,7 +14772,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>13</v>
       </c>
@@ -14791,7 +14795,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>13</v>
       </c>
@@ -14817,7 +14821,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>9</v>
       </c>
@@ -14840,7 +14844,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>8</v>
       </c>
@@ -14863,7 +14867,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>8</v>
       </c>
@@ -14886,7 +14890,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>9</v>
       </c>
@@ -14912,7 +14916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>13</v>
       </c>
@@ -14935,7 +14939,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>13</v>
       </c>
@@ -14961,7 +14965,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>9</v>
       </c>
@@ -14984,7 +14988,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>9</v>
       </c>
@@ -15010,7 +15014,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>13</v>
       </c>
@@ -15033,7 +15037,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>8</v>
       </c>
@@ -15056,7 +15060,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="522" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>9</v>
       </c>
@@ -15082,7 +15086,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="523" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>13</v>
       </c>
@@ -15105,7 +15109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>9</v>
       </c>
@@ -15131,7 +15135,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>13</v>
       </c>
@@ -15154,7 +15158,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>9</v>
       </c>
@@ -15180,7 +15184,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>13</v>
       </c>
@@ -15203,7 +15207,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="528" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>9</v>
       </c>
@@ -15229,7 +15233,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>13</v>
       </c>
@@ -15252,7 +15256,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>9</v>
       </c>
@@ -15278,7 +15282,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>13</v>
       </c>
@@ -15301,7 +15305,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>9</v>
       </c>
@@ -15327,7 +15331,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="533" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>13</v>
       </c>
@@ -15350,7 +15354,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>9</v>
       </c>
@@ -15376,7 +15380,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>13</v>
       </c>
@@ -15399,7 +15403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>9</v>
       </c>
@@ -15425,7 +15429,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>13</v>
       </c>
@@ -15448,7 +15452,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>13</v>
       </c>
@@ -15474,7 +15478,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="539" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>9</v>
       </c>
@@ -15497,7 +15501,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>9</v>
       </c>
@@ -15523,7 +15527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="541" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>13</v>
       </c>
@@ -15546,7 +15550,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>9</v>
       </c>
@@ -15572,7 +15576,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="543" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>13</v>
       </c>
@@ -15595,7 +15599,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>13</v>
       </c>
@@ -15621,7 +15625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>9</v>
       </c>
@@ -15644,7 +15648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>9</v>
       </c>
@@ -15670,7 +15674,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>13</v>
       </c>
@@ -15693,7 +15697,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>8</v>
       </c>
@@ -15716,7 +15720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>8</v>
       </c>
@@ -15739,7 +15743,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>9</v>
       </c>
@@ -15765,7 +15769,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>13</v>
       </c>
@@ -15788,7 +15792,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>8</v>
       </c>
@@ -15811,7 +15815,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>9</v>
       </c>
@@ -15837,7 +15841,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>13</v>
       </c>
@@ -15860,7 +15864,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="555" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>9</v>
       </c>
@@ -15886,7 +15890,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>13</v>
       </c>
@@ -15909,7 +15913,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>9</v>
       </c>
@@ -15935,7 +15939,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>13</v>
       </c>
@@ -15958,7 +15962,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>9</v>
       </c>
@@ -15984,7 +15988,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>13</v>
       </c>
@@ -16007,7 +16011,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>9</v>
       </c>
@@ -16033,7 +16037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>13</v>
       </c>
@@ -16056,7 +16060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>9</v>
       </c>
@@ -16082,7 +16086,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="564" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>13</v>
       </c>
@@ -16105,7 +16109,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>9</v>
       </c>
@@ -16131,7 +16135,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>13</v>
       </c>
@@ -16154,7 +16158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>9</v>
       </c>
@@ -16180,7 +16184,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="568" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>13</v>
       </c>
@@ -16203,7 +16207,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="569" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>8</v>
       </c>
@@ -16226,7 +16230,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>8</v>
       </c>
@@ -16249,7 +16253,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>9</v>
       </c>
@@ -16275,7 +16279,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>13</v>
       </c>
@@ -16298,7 +16302,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="573" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>9</v>
       </c>
@@ -16324,7 +16328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="574" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>13</v>
       </c>
@@ -16347,7 +16351,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>9</v>
       </c>
@@ -16373,7 +16377,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>13</v>
       </c>
@@ -16396,7 +16400,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="577" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>9</v>
       </c>
@@ -16422,7 +16426,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="578" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>13</v>
       </c>
@@ -16445,7 +16449,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="579" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>8</v>
       </c>
@@ -16468,7 +16472,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="580" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>9</v>
       </c>
@@ -16494,7 +16498,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="581" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>13</v>
       </c>
@@ -16517,7 +16521,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="582" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>9</v>
       </c>
@@ -16543,7 +16547,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="583" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>13</v>
       </c>
@@ -16566,7 +16570,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="584" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>9</v>
       </c>
@@ -16592,7 +16596,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="585" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>13</v>
       </c>
@@ -16615,7 +16619,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="586" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>9</v>
       </c>
@@ -16641,7 +16645,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="587" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>13</v>
       </c>
@@ -16664,7 +16668,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="588" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>9</v>
       </c>
@@ -16690,7 +16694,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="589" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>13</v>
       </c>
@@ -16713,7 +16717,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="590" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>9</v>
       </c>
@@ -16739,7 +16743,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="591" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>13</v>
       </c>
@@ -16762,7 +16766,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="592" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>9</v>
       </c>
@@ -16788,7 +16792,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="593" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>13</v>
       </c>
@@ -16811,7 +16815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="594" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>9</v>
       </c>
@@ -16837,7 +16841,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>13</v>
       </c>
@@ -16860,7 +16864,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>9</v>
       </c>
@@ -16886,7 +16890,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>13</v>
       </c>
@@ -16909,7 +16913,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="598" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>8</v>
       </c>
@@ -16932,7 +16936,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>8</v>
       </c>
@@ -16955,7 +16959,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>9</v>
       </c>
@@ -16981,7 +16985,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="601" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>13</v>
       </c>
@@ -17004,7 +17008,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="602" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>9</v>
       </c>
@@ -17030,7 +17034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="603" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>13</v>
       </c>
@@ -17053,7 +17057,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="604" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>8</v>
       </c>
@@ -17076,7 +17080,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>9</v>
       </c>
@@ -17102,7 +17106,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>13</v>
       </c>
@@ -17125,7 +17129,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="607" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>9</v>
       </c>
@@ -17151,7 +17155,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="608" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>13</v>
       </c>
@@ -17174,7 +17178,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="609" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>9</v>
       </c>
@@ -17200,7 +17204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="610" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>13</v>
       </c>
@@ -17223,7 +17227,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="611" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>9</v>
       </c>
@@ -17249,7 +17253,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="612" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>13</v>
       </c>
@@ -17272,7 +17276,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="613" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>9</v>
       </c>
@@ -17298,7 +17302,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="614" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>13</v>
       </c>
@@ -17321,7 +17325,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="615" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>9</v>
       </c>
@@ -17347,7 +17351,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="616" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>13</v>
       </c>
@@ -17370,7 +17374,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="617" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>9</v>
       </c>
@@ -17396,7 +17400,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="618" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>13</v>
       </c>
@@ -17419,7 +17423,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="619" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>9</v>
       </c>
@@ -17445,7 +17449,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="620" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>13</v>
       </c>
@@ -17468,7 +17472,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="621" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>8</v>
       </c>
@@ -17491,7 +17495,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="622" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>8</v>
       </c>
@@ -17514,7 +17518,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="623" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>9</v>
       </c>
@@ -17540,7 +17544,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="624" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>13</v>
       </c>
@@ -17563,7 +17567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="625" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>9</v>
       </c>
@@ -17589,7 +17593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="626" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>13</v>
       </c>
@@ -17612,7 +17616,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="627" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>9</v>
       </c>
@@ -17638,7 +17642,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>13</v>
       </c>
@@ -17661,7 +17665,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="629" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>9</v>
       </c>
@@ -17687,7 +17691,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="630" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>13</v>
       </c>
@@ -17710,7 +17714,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="631" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>8</v>
       </c>
@@ -17733,7 +17737,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="632" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>9</v>
       </c>
@@ -17759,7 +17763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="633" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>13</v>
       </c>
@@ -17782,7 +17786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="634" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>9</v>
       </c>
@@ -17808,7 +17812,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="635" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>13</v>
       </c>
@@ -17831,7 +17835,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="636" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>9</v>
       </c>
@@ -17857,7 +17861,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="637" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>13</v>
       </c>
@@ -17880,7 +17884,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="638" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>9</v>
       </c>
@@ -17906,7 +17910,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="639" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>13</v>
       </c>
@@ -17929,7 +17933,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="640" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>9</v>
       </c>
@@ -17955,7 +17959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="641" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>13</v>
       </c>
@@ -17978,7 +17982,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="642" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>9</v>
       </c>
@@ -18004,7 +18008,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="643" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>13</v>
       </c>
@@ -18027,7 +18031,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="644" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>9</v>
       </c>
@@ -18053,7 +18057,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="645" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>13</v>
       </c>
@@ -18076,7 +18080,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="646" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>9</v>
       </c>
@@ -18102,7 +18106,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="647" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>13</v>
       </c>
@@ -18125,7 +18129,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="648" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>9</v>
       </c>
@@ -18151,7 +18155,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="649" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>13</v>
       </c>
@@ -18174,7 +18178,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="650" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>9</v>
       </c>
@@ -18200,7 +18204,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="651" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>13</v>
       </c>
@@ -18223,7 +18227,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="652" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>8</v>
       </c>
@@ -18246,7 +18250,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="653" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>8</v>
       </c>
@@ -18269,7 +18273,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="654" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>9</v>
       </c>
@@ -18295,7 +18299,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="655" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>13</v>
       </c>
@@ -18318,7 +18322,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="656" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>9</v>
       </c>
@@ -18344,7 +18348,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="657" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>13</v>
       </c>
@@ -18367,7 +18371,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="658" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>8</v>
       </c>
@@ -18390,7 +18394,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="659" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>9</v>
       </c>
@@ -18416,7 +18420,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="660" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>13</v>
       </c>
@@ -18439,7 +18443,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="661" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>9</v>
       </c>
@@ -18465,7 +18469,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="662" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>13</v>
       </c>
@@ -18488,7 +18492,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="663" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>9</v>
       </c>
@@ -18514,7 +18518,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="664" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>13</v>
       </c>
@@ -18537,7 +18541,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="665" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>9</v>
       </c>
@@ -18563,7 +18567,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="666" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>13</v>
       </c>
@@ -18586,7 +18590,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="667" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>9</v>
       </c>
@@ -18612,7 +18616,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="668" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>13</v>
       </c>
@@ -18635,7 +18639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="669" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>9</v>
       </c>
@@ -18661,7 +18665,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="670" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>13</v>
       </c>
@@ -18684,7 +18688,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="671" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>9</v>
       </c>
@@ -18710,7 +18714,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="672" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>13</v>
       </c>
@@ -18733,7 +18737,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="673" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>9</v>
       </c>
@@ -18759,7 +18763,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="674" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>13</v>
       </c>
@@ -18782,7 +18786,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="675" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>8</v>
       </c>
@@ -18805,7 +18809,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="676" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>8</v>
       </c>
@@ -18828,7 +18832,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="677" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>9</v>
       </c>
@@ -18854,7 +18858,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="678" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>13</v>
       </c>
@@ -18877,7 +18881,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="679" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>9</v>
       </c>
@@ -18903,7 +18907,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="680" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>13</v>
       </c>
@@ -18926,7 +18930,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="681" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>8</v>
       </c>
@@ -18949,7 +18953,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="682" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>9</v>
       </c>
@@ -18975,7 +18979,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="683" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>13</v>
       </c>
@@ -18998,7 +19002,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="684" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>9</v>
       </c>
@@ -19024,7 +19028,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="685" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>13</v>
       </c>
@@ -19047,7 +19051,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="686" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>9</v>
       </c>
@@ -19073,7 +19077,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="687" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>13</v>
       </c>
@@ -19096,7 +19100,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="688" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>9</v>
       </c>
@@ -19122,7 +19126,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="689" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>13</v>
       </c>
@@ -19145,7 +19149,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="690" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>9</v>
       </c>
@@ -19171,7 +19175,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="691" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>13</v>
       </c>
@@ -19194,7 +19198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="692" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>9</v>
       </c>
@@ -19220,7 +19224,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="693" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>13</v>
       </c>
@@ -19243,7 +19247,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="694" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>8</v>
       </c>
@@ -19266,7 +19270,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="695" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>8</v>
       </c>
@@ -19289,7 +19293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="696" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>9</v>
       </c>
@@ -19315,7 +19319,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="697" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>13</v>
       </c>
@@ -19338,7 +19342,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="698" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>9</v>
       </c>
@@ -19364,7 +19368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="699" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>13</v>
       </c>
@@ -19387,7 +19391,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="700" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>9</v>
       </c>
@@ -19413,7 +19417,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="701" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>13</v>
       </c>
@@ -19436,7 +19440,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="702" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>8</v>
       </c>
@@ -19459,7 +19463,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="703" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>9</v>
       </c>
@@ -19485,7 +19489,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="704" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>13</v>
       </c>
@@ -19508,7 +19512,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="705" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>9</v>
       </c>
@@ -19534,7 +19538,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="706" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>13</v>
       </c>
@@ -19557,7 +19561,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="707" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>9</v>
       </c>
@@ -19583,7 +19587,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="708" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>13</v>
       </c>
@@ -19606,7 +19610,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="709" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>9</v>
       </c>
@@ -19632,7 +19636,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="710" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>13</v>
       </c>
@@ -19655,7 +19659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="711" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>9</v>
       </c>
@@ -19681,7 +19685,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="712" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>13</v>
       </c>
@@ -19704,7 +19708,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="713" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>9</v>
       </c>
@@ -19730,7 +19734,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="714" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>13</v>
       </c>
@@ -19753,7 +19757,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="715" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>8</v>
       </c>
@@ -19776,7 +19780,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="716" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>8</v>
       </c>
@@ -19799,7 +19803,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="717" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>9</v>
       </c>
@@ -19825,7 +19829,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="718" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>13</v>
       </c>
@@ -19848,7 +19852,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="719" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>8</v>
       </c>
@@ -19871,7 +19875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="720" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>9</v>
       </c>
@@ -19897,7 +19901,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="721" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>13</v>
       </c>
